--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB5C93F-5EA0-41BB-8539-E511A288E079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E82D8DE-668F-4D89-B47D-40090F16EBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="62">
   <si>
     <t>TPI - Journal de travail | Semaine 1 - Jeudi 23 - Vendredi 24 avril 2026</t>
   </si>
@@ -193,6 +193,51 @@
   </si>
   <si>
     <t>Envoie du rendu du vendredi du lien github par mail.</t>
+  </si>
+  <si>
+    <t>Rédaction de la documentation sur le point "Analyse des besoins" et délimitation du projet</t>
+  </si>
+  <si>
+    <t>Création des "chapitres" de la documentation. Création de la table des matières</t>
+  </si>
+  <si>
+    <t>Remplissage du journal de travail de ce matin</t>
+  </si>
+  <si>
+    <t>Conception</t>
+  </si>
+  <si>
+    <t>Création du schéma entité-relation sur draw.io (tables, attributs, relations entre entités)</t>
+  </si>
+  <si>
+    <t>Création du diagramme de flux de l'application sur draw.io (flux d'authentification, dashboards, actions utilisateur)</t>
+  </si>
+  <si>
+    <t>Rédaction des exigences fonctionnelles (EF-01 à EF-06) dans la documentation</t>
+  </si>
+  <si>
+    <t>Rédaction des exigences non fonctionnelles (ENF-01) dans la documentation</t>
+  </si>
+  <si>
+    <t>Amélioration du diagramme de flux sur draw.io, séparation des dashboards Admin et Utilisateur standard</t>
+  </si>
+  <si>
+    <t>Création des maquettes (wireframes) de l'application avec l'aide de l'IA</t>
+  </si>
+  <si>
+    <t>Rédaction de la déclaration d'utilisation de l'IA et structuration des annexes (glossaire, dépôt Git, sources)</t>
+  </si>
+  <si>
+    <t>Remplissage du journal de travail</t>
+  </si>
+  <si>
+    <t>Envoi du rendu du mardi aux experts et au chef de projet par mail</t>
+  </si>
+  <si>
+    <t>Mail de rendu</t>
+  </si>
+  <si>
+    <t>Amélioration de la maquette UI/UX</t>
   </si>
 </sst>
 </file>
@@ -818,11 +863,11 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="B8" s="9">
-        <v>0.68055555555555558</v>
+        <v>0.62152777777777779</v>
       </c>
       <c r="C8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>3:00</v>
+        <v>1:35</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>31</v>
@@ -832,34 +877,42 @@
       </c>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <f>IF(AND(A9&lt;&gt;"",B9&lt;&gt;""),TEXT(B9-A9,"[h]:mm"),"")</f>
+        <v>1:15</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
         <v>0.68402777777777779</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B10" s="9">
         <v>0.69444444444444442</v>
       </c>
-      <c r="C9" s="4" t="str">
+      <c r="C10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>0:15</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -869,7 +922,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
-        <v>6:55</v>
+        <v>6:45</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -1001,7 +1054,7 @@
         <v>0:10</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>46</v>
@@ -1047,7 +1100,7 @@
       <c r="B23" s="14"/>
       <c r="C23" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
-        <v>10:55</v>
+        <v>10:45</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1071,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -1103,7 +1156,7 @@
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1123,70 +1176,118 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.40972222222222221</v>
+      </c>
       <c r="C5" s="4" t="str">
         <f t="shared" ref="C5:C10" si="0">IF(AND(A5&lt;&gt;"",B5&lt;&gt;""),TEXT(B5-A5,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
+        <v>1:35</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C6" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
+        <v>2:25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.56944444444444442</v>
+      </c>
       <c r="C7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
+        <v>0:20</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+    <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.625</v>
+      </c>
       <c r="C8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
+        <v>1:15</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+    <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.68402777777777779</v>
+      </c>
       <c r="C9" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
+        <v>1:20</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+    <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="C10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
+        <v>0:15</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1196,7 +1297,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>7:10</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -1220,7 +1321,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -1240,139 +1341,195 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+    <row r="15" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="C15" s="4" t="str">
-        <f t="shared" ref="C15:C20" si="1">IF(AND(A15&lt;&gt;"",B15&lt;&gt;""),TEXT(B15-A15,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
+        <f t="shared" ref="C15:C21" si="1">IF(AND(A15&lt;&gt;"",B15&lt;&gt;""),TEXT(B15-A15,"[h]:mm"),"")</f>
+        <v>1:15</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+    <row r="16" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="B16" s="9">
+        <v>0.4375</v>
+      </c>
       <c r="C16" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
+        <v>0:55</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+    <row r="17" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C17" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
+        <v>1:55</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+    <row r="18" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="C18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
+        <v>1:10</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+      <c r="A19" s="9">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0.62152777777777779</v>
+      </c>
       <c r="C19" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
+        <v>0:20</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0.68055555555555558</v>
+      </c>
       <c r="C20" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
+        <v>1:15</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+    <row r="21" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="C21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>0:15</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="4" t="str">
-        <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
-        <v>0:00</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="B22" s="12"/>
+      <c r="C22" s="4" t="str">
+        <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
+        <v>5:50</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+    </row>
+    <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4" t="str">
-        <f t="shared" ref="C25:C30" si="2">IF(AND(A25&lt;&gt;"",B25&lt;&gt;""),TEXT(B25-A25,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C26:C31" si="2">IF(AND(A26&lt;&gt;"",B26&lt;&gt;""),TEXT(B26-A26,"[h]:mm"),"")</f>
         <v/>
       </c>
       <c r="D26" s="5"/>
@@ -1424,72 +1581,72 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="4" t="str">
-        <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
+      <c r="B32" s="12"/>
+      <c r="C32" s="4" t="str">
+        <f>TEXT(IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>0:00</v>
       </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+    </row>
+    <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+    </row>
+    <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4" t="str">
-        <f t="shared" ref="C35:C40" si="3">IF(AND(A35&lt;&gt;"",B35&lt;&gt;""),TEXT(B35-A35,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="C36:C41" si="3">IF(AND(A36&lt;&gt;"",B36&lt;&gt;""),TEXT(B36-A36,"[h]:mm"),"")</f>
         <v/>
       </c>
       <c r="D36" s="5"/>
@@ -1541,55 +1698,66 @@
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="4" t="str">
-        <f>TEXT(IF(C35&lt;&gt;"",TIMEVALUE(C35),0)+IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0),"[h]:mm")</f>
+      <c r="B42" s="12"/>
+      <c r="C42" s="4" t="str">
+        <f>TEXT(IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>0:00</v>
       </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-    </row>
-    <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+    </row>
+    <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="8" t="str">
-        <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
-        <v>0:00</v>
-      </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="8" t="str">
+        <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0)+IF(C32&lt;&gt;"",TIMEVALUE(C32),0)+IF(C42&lt;&gt;"",TIMEVALUE(C42),0),"[h]:mm")</f>
+        <v>13:00</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E82D8DE-668F-4D89-B47D-40090F16EBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E46DF-4244-48DB-A0EC-7A32A1C39318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="15360" windowHeight="15585" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="71">
   <si>
     <t>TPI - Journal de travail | Semaine 1 - Jeudi 23 - Vendredi 24 avril 2026</t>
   </si>
@@ -238,6 +238,33 @@
   </si>
   <si>
     <t>Amélioration de la maquette UI/UX</t>
+  </si>
+  <si>
+    <t>Lecture de la documentation Supabase et streamlit pour la reprise (pour me rafraichir la mémoire)</t>
+  </si>
+  <si>
+    <t>Implémentation</t>
+  </si>
+  <si>
+    <t>Initialisation de la connexion Supabase</t>
+  </si>
+  <si>
+    <t>L'interface Supabase a changé, la configuration a pris plus de temps que prévu</t>
+  </si>
+  <si>
+    <t>Création de la structure des fichiers du projet</t>
+  </si>
+  <si>
+    <t>Revue du fonctionnement de Streamlit et tests de composants</t>
+  </si>
+  <si>
+    <t>Visionnage de vidéos YouTube sur l'intégration Supabase avec Python (authentification, requêtes)</t>
+  </si>
+  <si>
+    <t>Prise de notes et réflexion sur la structure des pages Streamlit à implémenter</t>
+  </si>
+  <si>
+    <t>Push du repo github, relecture et envoie du mail de rendu</t>
   </si>
 </sst>
 </file>
@@ -1525,48 +1552,82 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+    <row r="26" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0.40972222222222221</v>
+      </c>
       <c r="C26" s="4" t="str">
         <f t="shared" ref="C26:C31" si="2">IF(AND(A26&lt;&gt;"",B26&lt;&gt;""),TEXT(B26-A26,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
+        <v>1:35</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="F26" s="6"/>
     </row>
     <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+      <c r="A27" s="9">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0.4375</v>
+      </c>
       <c r="C27" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
+        <v>0:25</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+    <row r="28" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C28" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+        <v>2:00</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+      <c r="A29" s="9">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="C29" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
+        <v>3:20</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1598,7 +1659,7 @@
       <c r="B32" s="12"/>
       <c r="C32" s="4" t="str">
         <f>TEXT(IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>7:20</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -1642,59 +1703,99 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
+    <row r="36" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0.40972222222222221</v>
+      </c>
       <c r="C36" s="4" t="str">
         <f t="shared" ref="C36:C41" si="3">IF(AND(A36&lt;&gt;"",B36&lt;&gt;""),TEXT(B36-A36,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="6"/>
+        <v>1:35</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
+    <row r="37" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="B37" s="9">
+        <v>0.4861111111111111</v>
+      </c>
       <c r="C37" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="6"/>
+        <v>1:35</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
+      <c r="A38" s="9">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.5</v>
+      </c>
       <c r="C38" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
+        <v>0:15</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+    <row r="39" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="B39" s="9">
+        <v>0.51388888888888884</v>
+      </c>
       <c r="C39" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="6"/>
+        <v>0:20</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C40" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="6"/>
+        <v>0:10</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1715,7 +1816,7 @@
       <c r="B42" s="12"/>
       <c r="C42" s="4" t="str">
         <f>TEXT(IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>3:55</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -1736,7 +1837,7 @@
       <c r="B44" s="14"/>
       <c r="C44" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0)+IF(C32&lt;&gt;"",TIMEVALUE(C32),0)+IF(C42&lt;&gt;"",TIMEVALUE(C42),0),"[h]:mm")</f>
-        <v>13:00</v>
+        <v>24:15</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>

--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E46DF-4244-48DB-A0EC-7A32A1C39318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6523ACF-0FC7-4321-8537-28D2867C4967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="15360" windowHeight="15585" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="81">
   <si>
     <t>TPI - Journal de travail | Semaine 1 - Jeudi 23 - Vendredi 24 avril 2026</t>
   </si>
@@ -265,6 +265,36 @@
   </si>
   <si>
     <t>Push du repo github, relecture et envoie du mail de rendu</t>
+  </si>
+  <si>
+    <t>Je suis arrivé en retard car je me suis rendormi</t>
+  </si>
+  <si>
+    <t>Correction des imports / renommage fichiers</t>
+  </si>
+  <si>
+    <t>Système d'authentification (bcrypt, session, cookies, role), ajout des utilisateurs dans la db</t>
+  </si>
+  <si>
+    <t>Développement de la structure de base de la page equipments.py : header avec titre, colonnes, boutons d'action (CSV, Scan, Add device)</t>
+  </si>
+  <si>
+    <t>Développement du formulaire d'ajout manuel via st.dialog : 10 champs de saisie, soumission avec gestion d'erreur try/except. Débogage de l'erreur de virgules trailing (tuples Python au lieu de strings)</t>
+  </si>
+  <si>
+    <t>Débogage de l'erreur de type integer côté Supabase : correction de la conversion des champs optionnels vides en None (warranty_months, assigned_user_id, purchase_date)</t>
+  </si>
+  <si>
+    <t>Développement de la barre de filtres (type, statut, tri warranty) et du bouton Reset. Implémentation de la logique de filtrage cumulatif par list comprehension</t>
+  </si>
+  <si>
+    <t>Développement du dashboard : métriques par statut avec st.metric, graphique à barres (répartition par type) et diagramme circulaire (répartition par statut) avec Plotly Express</t>
+  </si>
+  <si>
+    <t>Développement de l'affichage des équipements : cards HTML custom via st.markdown avec badges de statut colorés dynamiquement selon un dictionnaire de couleurs</t>
+  </si>
+  <si>
+    <t>Rédaction des sections front-end, back-end, concept de rôles et authentification dans la documentation TPI</t>
   </si>
 </sst>
 </file>
@@ -460,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -509,6 +539,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1845,6 +1878,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F24"/>
@@ -1854,11 +1892,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1917,59 +1950,101 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.40972222222222221</v>
+      </c>
       <c r="C5" s="4" t="str">
         <f t="shared" ref="C5:C10" si="0">IF(AND(A5&lt;&gt;"",B5&lt;&gt;""),TEXT(B5-A5,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+        <v>0:20</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C6" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
+        <v>2:25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.61805555555555558</v>
+      </c>
       <c r="C7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
+        <v>1:30</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+    <row r="8" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>0.62152777777777779</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.68055555555555558</v>
+      </c>
       <c r="C8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
+        <v>1:25</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="9">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="C9" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
+        <v>0:20</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1990,7 +2065,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>6:00</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -2034,70 +2109,118 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+    <row r="15" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>0.34375</v>
+      </c>
+      <c r="B15" s="19">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="C15" s="4" t="str">
         <f t="shared" ref="C15:C20" si="1">IF(AND(A15&lt;&gt;"",B15&lt;&gt;""),TEXT(B15-A15,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
+        <v>1:15</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+    <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="B16" s="19">
+        <v>0.4513888888888889</v>
+      </c>
       <c r="C16" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
+        <v>1:15</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+    <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="B17" s="19">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C17" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
+        <v>1:40</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+    <row r="18" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B18" s="19">
+        <v>0.62152777777777779</v>
+      </c>
       <c r="C18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
+        <v>1:35</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+    <row r="19" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B19" s="19">
+        <v>0.69097222222222221</v>
+      </c>
       <c r="C19" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
+        <v>1:30</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+    <row r="20" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="B20" s="19">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="C20" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
+        <v>0:05</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2107,7 +2230,7 @@
       <c r="B21" s="12"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>7:20</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -2362,7 +2485,7 @@
       <c r="B43" s="14"/>
       <c r="C43" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>13:20</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -2370,6 +2493,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
@@ -2379,11 +2507,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2681,16 +2804,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3085,17 +3208,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6523ACF-0FC7-4321-8537-28D2867C4967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080DAFD9-57F6-4970-85B4-52D658471D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="Semaine 4" sheetId="5" r:id="rId4"/>
     <sheet name="Semaine 5" sheetId="6" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semaine 3'!$A$1:$F$43</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,15 +35,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>TPI - Journal de travail | Semaine 1 - Jeudi 23 - Vendredi 24 avril 2026</t>
   </si>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>Ma 19.05.2026 - Mardi</t>
-  </si>
-  <si>
-    <t>Je 23.04.2026 - Vendredi</t>
   </si>
   <si>
     <r>
@@ -295,6 +292,42 @@
   </si>
   <si>
     <t>Rédaction des sections front-end, back-end, concept de rôles et authentification dans la documentation TPI</t>
+  </si>
+  <si>
+    <t>Je 23.04.2026 - Jeudi</t>
+  </si>
+  <si>
+    <t>Gestion des équipements : implémentation du reset des filtres avec session_state et correction des selectbox</t>
+  </si>
+  <si>
+    <t>Gestion des équipements : création des cards cliquables avec st.columns et bouton info par device</t>
+  </si>
+  <si>
+    <t>Gestion des équipements : implémentation du dialog show_device_info et correction de bugs (TypeError, len())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification et amélioration de la fonction global search pour les équipements dans la database. </t>
+  </si>
+  <si>
+    <t>Gestion des équipements : implémentation deglobal search avec text_input et requête .or_() sur Supabase</t>
+  </si>
+  <si>
+    <t>Revue</t>
+  </si>
+  <si>
+    <t>Discussion avec le chef de projet pour voir si tout allait bien ou non.</t>
+  </si>
+  <si>
+    <t>Dashboard : implémentation des métriques, graphiques Plotly et cards HTML pour équipements et utilisateurs</t>
+  </si>
+  <si>
+    <t>Navigation : correction erreur st.page_link pour rôle standard et affichage du username connecté dans la sidebar</t>
+  </si>
+  <si>
+    <t>Rédaction des sources et références (annexes) et complétion du journal de travail</t>
+  </si>
+  <si>
+    <t>Modification des fonctions get user info et correction des bugs d'affichage du nombre de users affichés.</t>
   </si>
 </sst>
 </file>
@@ -521,6 +554,9 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="21" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -539,9 +575,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -819,25 +852,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="A3" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -871,13 +904,13 @@
         <v>0:30</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -892,10 +925,10 @@
         <v>0:45</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="6"/>
     </row>
@@ -904,17 +937,17 @@
         <v>0.4201388888888889</v>
       </c>
       <c r="B7" s="9">
-        <v>0.52083333333333337</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="C7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>2:25</v>
+        <v>0:40</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="6"/>
     </row>
@@ -930,10 +963,10 @@
         <v>1:35</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" s="6"/>
     </row>
@@ -949,10 +982,10 @@
         <v>1:15</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="6"/>
     </row>
@@ -968,43 +1001,43 @@
         <v>0:15</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>37</v>
-      </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
-        <v>6:45</v>
+        <v>5:00</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1038,10 +1071,10 @@
         <v>0:15</v>
       </c>
       <c r="D15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>40</v>
       </c>
       <c r="F15" s="6"/>
     </row>
@@ -1057,10 +1090,10 @@
         <v>0:30</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" s="6"/>
     </row>
@@ -1076,10 +1109,10 @@
         <v>0:50</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="6"/>
     </row>
@@ -1095,10 +1128,10 @@
         <v>2:15</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="F18" s="6"/>
     </row>
@@ -1114,10 +1147,10 @@
         <v>0:10</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F19" s="6"/>
     </row>
@@ -1133,10 +1166,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="12"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>4:00</v>
@@ -1146,21 +1179,21 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="14"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
-        <v>10:45</v>
+        <v>9:00</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1196,25 +1229,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1248,10 +1281,10 @@
         <v>1:35</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -1267,10 +1300,10 @@
         <v>2:25</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" s="6"/>
     </row>
@@ -1286,10 +1319,10 @@
         <v>0:20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="6"/>
     </row>
@@ -1305,10 +1338,10 @@
         <v>1:15</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="F8" s="6"/>
     </row>
@@ -1324,10 +1357,10 @@
         <v>1:20</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="6"/>
     </row>
@@ -1343,18 +1376,18 @@
         <v>0:15</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>7:10</v>
@@ -1364,22 +1397,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1413,10 +1446,10 @@
         <v>1:15</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F15" s="6"/>
     </row>
@@ -1432,10 +1465,10 @@
         <v>0:55</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" s="6"/>
     </row>
@@ -1451,10 +1484,10 @@
         <v>1:55</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" s="6"/>
     </row>
@@ -1470,10 +1503,10 @@
         <v>1:10</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F18" s="6"/>
     </row>
@@ -1489,10 +1522,10 @@
         <v>0:20</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F19" s="6"/>
     </row>
@@ -1508,10 +1541,10 @@
         <v>1:15</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="6"/>
     </row>
@@ -1527,18 +1560,18 @@
         <v>0:15</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="12"/>
+      <c r="B22" s="13"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>5:50</v>
@@ -1548,22 +1581,22 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
     </row>
     <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -1597,10 +1630,10 @@
         <v>1:35</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F26" s="6"/>
     </row>
@@ -1609,39 +1642,39 @@
         <v>0.4201388888888889</v>
       </c>
       <c r="B27" s="9">
-        <v>0.4375</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="C27" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>0:25</v>
+        <v>0:10</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
-        <v>0.4375</v>
+        <v>0.42708333333333331</v>
       </c>
       <c r="B28" s="9">
-        <v>0.52083333333333337</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="C28" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>2:00</v>
+        <v>0:30</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1656,10 +1689,10 @@
         <v>3:20</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F29" s="6"/>
     </row>
@@ -1686,35 +1719,35 @@
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="12"/>
+      <c r="B32" s="13"/>
       <c r="C32" s="4" t="str">
         <f>TEXT(IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
-        <v>7:20</v>
+        <v>5:35</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -1748,10 +1781,10 @@
         <v>1:35</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F36" s="6"/>
     </row>
@@ -1767,10 +1800,10 @@
         <v>1:35</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F37" s="6"/>
     </row>
@@ -1786,10 +1819,10 @@
         <v>0:15</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F38" s="6"/>
     </row>
@@ -1805,10 +1838,10 @@
         <v>0:20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F39" s="6"/>
     </row>
@@ -1824,10 +1857,10 @@
         <v>0:10</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="6"/>
     </row>
@@ -1843,10 +1876,10 @@
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="12"/>
+      <c r="B42" s="13"/>
       <c r="C42" s="4" t="str">
         <f>TEXT(IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -1856,21 +1889,21 @@
       <c r="F42" s="7"/>
     </row>
     <row r="43" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="14"/>
+      <c r="B44" s="15"/>
       <c r="C44" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0)+IF(C32&lt;&gt;"",TIMEVALUE(C32),0)+IF(C42&lt;&gt;"",TIMEVALUE(C42),0),"[h]:mm")</f>
-        <v>24:15</v>
+        <v>22:30</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -1910,25 +1943,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1962,13 +1995,13 @@
         <v>0:20</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -1983,10 +2016,10 @@
         <v>2:25</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6" s="6"/>
     </row>
@@ -2002,10 +2035,10 @@
         <v>1:30</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="6"/>
     </row>
@@ -2021,10 +2054,10 @@
         <v>1:25</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="6"/>
     </row>
@@ -2040,10 +2073,10 @@
         <v>0:20</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="6"/>
     </row>
@@ -2059,10 +2092,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>6:00</v>
@@ -2072,22 +2105,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2110,10 +2143,10 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+      <c r="A15" s="12">
         <v>0.34375</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="12">
         <v>0.39583333333333331</v>
       </c>
       <c r="C15" s="4" t="str">
@@ -2121,18 +2154,18 @@
         <v>1:15</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="A16" s="12">
         <v>0.39930555555555558</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="12">
         <v>0.4513888888888889</v>
       </c>
       <c r="C16" s="4" t="str">
@@ -2140,18 +2173,18 @@
         <v>1:15</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+      <c r="A17" s="12">
         <v>0.4513888888888889</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="12">
         <v>0.52083333333333337</v>
       </c>
       <c r="C17" s="4" t="str">
@@ -2159,18 +2192,18 @@
         <v>1:40</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+      <c r="A18" s="12">
         <v>0.55555555555555558</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="12">
         <v>0.62152777777777779</v>
       </c>
       <c r="C18" s="4" t="str">
@@ -2178,18 +2211,18 @@
         <v>1:35</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+      <c r="A19" s="12">
         <v>0.62847222222222221</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="12">
         <v>0.69097222222222221</v>
       </c>
       <c r="C19" s="4" t="str">
@@ -2197,18 +2230,18 @@
         <v>1:30</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+      <c r="A20" s="12">
         <v>0.69097222222222221</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="12">
         <v>0.69444444444444442</v>
       </c>
       <c r="C20" s="4" t="str">
@@ -2216,18 +2249,18 @@
         <v>0:05</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="12"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>7:20</v>
@@ -2237,22 +2270,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -2274,104 +2307,152 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+    <row r="25" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0.37847222222222232</v>
+      </c>
       <c r="C25" s="4" t="str">
         <f t="shared" ref="C25:C30" si="2">IF(AND(A25&lt;&gt;"",B25&lt;&gt;""),TEXT(B25-A25,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
+        <v>0:50</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+    <row r="26" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0.4201388888888889</v>
+      </c>
       <c r="C26" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
+        <v>0:55</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+    <row r="27" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="C27" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
+        <v>0:50</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+    <row r="28" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0.48958333333333331</v>
+      </c>
       <c r="C28" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="6"/>
+        <v>0:40</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+    <row r="29" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0.62152777777777779</v>
+      </c>
       <c r="C29" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
+        <v>1:35</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+    <row r="30" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="C30" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="6"/>
+        <v>1:35</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="12"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>6:25</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+    </row>
+    <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>1</v>
       </c>
@@ -2391,59 +2472,99 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+    <row r="35" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="B35" s="9">
+        <v>0.35416666666666669</v>
+      </c>
       <c r="C35" s="4" t="str">
         <f t="shared" ref="C35:C40" si="3">IF(AND(A35&lt;&gt;"",B35&lt;&gt;""),TEXT(B35-A35,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="6"/>
+        <v>0:15</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
+    <row r="36" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="9">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0.40972222222222221</v>
+      </c>
       <c r="C36" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="6"/>
+        <v>1:20</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
+    <row r="37" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="B37" s="9">
+        <v>0.47222222222222221</v>
+      </c>
       <c r="C37" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="6"/>
+        <v>1:15</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
+    <row r="38" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="9">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.48958333333333331</v>
+      </c>
       <c r="C38" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
+        <v>0:25</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+    <row r="39" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="B39" s="9">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C39" s="4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="6"/>
+        <v>0:40</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2458,34 +2579,34 @@
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="12"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="4" t="str">
         <f>TEXT(IF(C35&lt;&gt;"",TIMEVALUE(C35),0)+IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>3:55</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="14"/>
+      <c r="B43" s="15"/>
       <c r="C43" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
-        <v>13:20</v>
+        <v>23:40</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -2508,8 +2629,8 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2525,25 +2646,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2632,10 +2753,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -2645,22 +2766,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2749,10 +2870,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="12"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -2762,38 +2883,38 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="14"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -2832,25 +2953,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2939,10 +3060,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -2952,22 +3073,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -3056,10 +3177,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="12"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3069,22 +3190,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
+      <c r="A23" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -3173,10 +3294,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="12"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3186,18 +3307,18 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="14"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>0:00</v>

--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080DAFD9-57F6-4970-85B4-52D658471D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE37258D-BEAD-40E7-8179-324CBCAB4AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Semaine 3'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Semaine 4'!$A$1:$F$26</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="108">
   <si>
     <t>TPI - Journal de travail | Semaine 1 - Jeudi 23 - Vendredi 24 avril 2026</t>
   </si>
@@ -329,12 +330,63 @@
   <si>
     <t>Modification des fonctions get user info et correction des bugs d'affichage du nombre de users affichés.</t>
   </si>
+  <si>
+    <t>Développement</t>
+  </si>
+  <si>
+    <t>Analyse et amélioration de la fonction update_user : passage au filtrage par id immuable, ajout d'une valeur de retour et d'une gestion d'erreur explicite</t>
+  </si>
+  <si>
+    <t>Débogage</t>
+  </si>
+  <si>
+    <t>Identification du bug TypeError 'list indices must be integers or slices, not str' dans db_users.py : retour Supabase sous forme de liste même pour un seul résultat</t>
+  </si>
+  <si>
+    <t>Correction du bug via user[0]["id"] et du passage incorrect de new_username dans edit_user() (pages/users.py), tests de validation des corrections</t>
+  </si>
+  <si>
+    <t>Remplissage du journal de travail de la matinée</t>
+  </si>
+  <si>
+    <t>Visite du 2ème expert : présentation de l'avancement du projet et échanges</t>
+  </si>
+  <si>
+    <t>Correction de la fonction de modification d'un utilisateur (username et role) : gestion du retour liste Supabase, filtrage par id, tests</t>
+  </si>
+  <si>
+    <t>Relecture</t>
+  </si>
+  <si>
+    <t>Amélioration de la page users.py : analyse du flux de données entre la boucle for, show_user_info() et edit_user() via st.session_state</t>
+  </si>
+  <si>
+    <t>Implémentation du bouton de confirmation de suppression d'un utilisateur avec flag dans st.session_state</t>
+  </si>
+  <si>
+    <t>Implémentation du bouton CSV : fonction generate_csv() avec io.StringIO et csv.DictWriter, export des équipements filtrés</t>
+  </si>
+  <si>
+    <t>Correction du bug double bouton CSV causé par st.empty() : déplacement du st.download_button après le bloc de filtres pour accéder à filtred_equipments</t>
+  </si>
+  <si>
+    <t>Remplissage du journal de travail et ajout de commentaires en anglais sur la fonction generate_csv()</t>
+  </si>
+  <si>
+    <t>Relecture du code, de ce qui est fait, de ce qui doit etre fait et des améliorations possibles</t>
+  </si>
+  <si>
+    <t>Amélioration de l'affichage UI de show_device_info : mise en page markdown avec grille 2 colonnes, serial number sous le nom, badge de statut coloré</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="h:mm"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,6 +461,12 @@
       <color rgb="FF1E2A38"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -523,7 +581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -555,6 +613,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -852,25 +919,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-    </row>
-    <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1009,10 +1075,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>5:00</v>
@@ -1021,23 +1087,23 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1166,10 +1232,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="13"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>4:00</v>
@@ -1178,19 +1244,19 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="15"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>9:00</v>
@@ -1229,25 +1295,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-    </row>
-    <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+    </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1384,10 +1449,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>7:10</v>
@@ -1396,23 +1461,23 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1568,10 +1633,10 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="13"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>5:50</v>
@@ -1580,23 +1645,23 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -1719,10 +1784,10 @@
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="13"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="4" t="str">
         <f>TEXT(IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>5:35</v>
@@ -1731,23 +1796,23 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -1876,10 +1941,10 @@
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="13"/>
+      <c r="B42" s="16"/>
       <c r="C42" s="4" t="str">
         <f>TEXT(IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -1888,19 +1953,19 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="15"/>
+      <c r="B44" s="18"/>
       <c r="C44" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0)+IF(C32&lt;&gt;"",TIMEVALUE(C32),0)+IF(C42&lt;&gt;"",TIMEVALUE(C42),0),"[h]:mm")</f>
         <v>22:30</v>
@@ -1943,25 +2008,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2092,10 +2157,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>6:00</v>
@@ -2104,23 +2169,23 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2257,10 +2322,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="13"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>7:20</v>
@@ -2269,23 +2334,23 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -2422,10 +2487,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="13"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>6:25</v>
@@ -2434,23 +2499,23 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
     </row>
     <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -2579,10 +2644,10 @@
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="13"/>
+      <c r="B41" s="16"/>
       <c r="C41" s="4" t="str">
         <f>TEXT(IF(C35&lt;&gt;"",TIMEVALUE(C35),0)+IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -2591,19 +2656,19 @@
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="15"/>
+      <c r="B43" s="18"/>
       <c r="C43" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>23:40</v>
@@ -2636,7 +2701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
@@ -2646,25 +2711,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2686,258 +2751,374 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
+        <v>0.34375</v>
+      </c>
+      <c r="B5" s="14">
+        <v>0.39583333333333298</v>
+      </c>
       <c r="C5" s="4" t="str">
-        <f t="shared" ref="C5:C10" si="0">IF(AND(A5&lt;&gt;"",B5&lt;&gt;""),TEXT(B5-A5,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
+        <f t="shared" ref="C5:C11" si="0">IF(AND(A5&lt;&gt;"",B5&lt;&gt;""),TEXT(B5-A5,"[h]:mm"),"")</f>
+        <v>1:15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>93</v>
+      </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+    <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="B6" s="14">
+        <v>0.4375</v>
+      </c>
       <c r="C6" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
+        <v>1:00</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>0.4375</v>
+      </c>
+      <c r="B7" s="14">
+        <v>0.46875</v>
+      </c>
       <c r="C7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
+        <v>0:45</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <v>0.55555555555555602</v>
+      </c>
+      <c r="B8" s="14">
+        <v>0.56944444444444398</v>
+      </c>
       <c r="C8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
+        <v>0:20</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>97</v>
+      </c>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+    <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <v>0.56944444444444398</v>
+      </c>
+      <c r="B9" s="14">
+        <v>0.58333333333333304</v>
+      </c>
       <c r="C9" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
+        <v>0:20</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>98</v>
+      </c>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+    <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="B10" s="14">
+        <v>0.62152777777777779</v>
+      </c>
       <c r="C10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
+        <v>0:55</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>99</v>
+      </c>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>0:25</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="4" t="str">
+      <c r="B12" s="16"/>
+      <c r="C12" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
-        <v>0:00</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>22</v>
-      </c>
+        <v>4:35</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
     </row>
-    <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4" t="str">
-        <f t="shared" ref="C15:C20" si="1">IF(AND(A15&lt;&gt;"",B15&lt;&gt;""),TEXT(B15-A15,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+    <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>0.34375</v>
+      </c>
+      <c r="B16" s="15">
+        <v>0.39583333333333298</v>
+      </c>
       <c r="C16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
+        <f t="shared" ref="C16:C21" si="1">IF(AND(A16&lt;&gt;"",B16&lt;&gt;""),TEXT(B16-A16,"[h]:mm"),"")</f>
+        <v>1:15</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+    <row r="17" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="B17" s="15">
+        <v>0.4375</v>
+      </c>
       <c r="C17" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
+        <v>1:00</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+    <row r="18" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>0.4375</v>
+      </c>
+      <c r="B18" s="15">
+        <v>0.5</v>
+      </c>
       <c r="C18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
+        <v>1:30</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+    <row r="19" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="B19" s="15">
+        <v>0.60416666666666696</v>
+      </c>
       <c r="C19" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
+        <v>1:30</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+    <row r="20" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="B20" s="15">
+        <v>0.64583333333333304</v>
+      </c>
       <c r="C20" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
+        <v>1:00</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="B21" s="15">
+        <v>0.69444444444444398</v>
+      </c>
+      <c r="C21" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>1:10</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="4" t="str">
-        <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
-        <v>0:00</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="4" t="str">
+        <f>TEXT(IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
+        <v>7:25</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+    </row>
+    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-    </row>
-    <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="8" t="str">
-        <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
-        <v>0:00</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="8" t="str">
+        <f>TEXT(IF(C12&lt;&gt;"",TIMEVALUE(C12),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0),"[h]:mm")</f>
+        <v>12:00</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2953,25 +3134,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3060,10 +3241,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="13"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3073,22 +3254,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -3177,10 +3358,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="13"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3190,22 +3371,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -3294,10 +3475,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="13"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3307,18 +3488,18 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="15"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>0:00</v>

--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -624,20 +624,20 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -919,24 +919,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1075,10 +1075,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="16"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>5:00</v>
@@ -1088,22 +1088,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1232,10 +1232,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="16"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>4:00</v>
@@ -1245,18 +1245,18 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="18"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>9:00</v>
@@ -1295,24 +1295,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1449,10 +1449,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="16"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>7:10</v>
@@ -1462,22 +1462,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1633,10 +1633,10 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="16"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>5:50</v>
@@ -1646,22 +1646,22 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
     </row>
     <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -1784,10 +1784,10 @@
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="16"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="4" t="str">
         <f>TEXT(IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>5:35</v>
@@ -1797,22 +1797,22 @@
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -1941,10 +1941,10 @@
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="16"/>
+      <c r="B42" s="17"/>
       <c r="C42" s="4" t="str">
         <f>TEXT(IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -1954,18 +1954,18 @@
       <c r="F42" s="7"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="18"/>
+      <c r="B44" s="16"/>
       <c r="C44" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0)+IF(C32&lt;&gt;"",TIMEVALUE(C32),0)+IF(C42&lt;&gt;"",TIMEVALUE(C42),0),"[h]:mm")</f>
         <v>22:30</v>
@@ -1976,11 +1976,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F24"/>
@@ -1990,6 +1985,11 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2008,25 +2008,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2157,10 +2157,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="16"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>6:00</v>
@@ -2170,22 +2170,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2322,10 +2322,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="16"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>7:20</v>
@@ -2335,22 +2335,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -2487,10 +2487,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="16"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>6:25</v>
@@ -2500,22 +2500,22 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -2644,10 +2644,10 @@
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="16"/>
+      <c r="B41" s="17"/>
       <c r="C41" s="4" t="str">
         <f>TEXT(IF(C35&lt;&gt;"",TIMEVALUE(C35),0)+IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -2657,18 +2657,18 @@
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="18"/>
+      <c r="B43" s="16"/>
       <c r="C43" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>23:40</v>
@@ -2679,11 +2679,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
@@ -2693,6 +2688,11 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2711,25 +2711,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2885,10 +2885,10 @@
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="16"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>4:35</v>
@@ -2898,22 +2898,22 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -3050,10 +3050,10 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="16"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>7:25</v>
@@ -3063,38 +3063,38 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="18"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="8" t="str">
         <f>TEXT(IF(C12&lt;&gt;"",TIMEVALUE(C12),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0),"[h]:mm")</f>
         <v>12:00</v>
@@ -3105,16 +3105,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3134,25 +3134,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3241,10 +3241,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="16"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3254,22 +3254,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -3358,10 +3358,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="16"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3371,22 +3371,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -3475,10 +3475,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="16"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3488,18 +3488,18 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="18"/>
+      <c r="B33" s="16"/>
       <c r="C33" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3510,17 +3510,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE37258D-BEAD-40E7-8179-324CBCAB4AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36174463-D009-48CC-AF56-F89C73B040EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Semaine 3'!$A$1:$F$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Semaine 4'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Semaine 5'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="123">
   <si>
     <t>TPI - Journal de travail | Semaine 1 - Jeudi 23 - Vendredi 24 avril 2026</t>
   </si>
@@ -378,6 +379,51 @@
   <si>
     <t>Amélioration de l'affichage UI de show_device_info : mise en page markdown avec grille 2 colonnes, serial number sous le nom, badge de statut coloré</t>
   </si>
+  <si>
+    <t>Finalisation de la page equipments.py : tri par garantie via sorted() et relativedelta, affichage des jours restants avec code couleur</t>
+  </si>
+  <si>
+    <t>Implémentation du bouton Reset des filtres via on_click, correction du bug multiselect (list → string), correction sérialisation date (.isoformat())</t>
+  </si>
+  <si>
+    <t>Aide IA : débogage erreurs de type</t>
+  </si>
+  <si>
+    <t>Implémentation de l'export CSV en mémoire via io.StringIO, tests de téléchargement avec filtres actifs</t>
+  </si>
+  <si>
+    <t>Implémentation de la page users.py : affichage, filtres, dialogs add/edit/show, gestion des rôles</t>
+  </si>
+  <si>
+    <t>Mise en place de db_users.py avec hachage bcrypt, tests de création et modification d'utilisateurs</t>
+  </si>
+  <si>
+    <t>Création de utils/logger.py : fonction log_action() centralisée. Intégration dans db_equipements.py (create, update avec détection des champs modifiés, delete)</t>
+  </si>
+  <si>
+    <t>Aide IA : structure du système de logs</t>
+  </si>
+  <si>
+    <t>Intégration des logs dans db_users.py (create_user, update_user, update_password, delete_user). Mise à jour de la contrainte CHECK de la table activity_logs</t>
+  </si>
+  <si>
+    <t>Correction de plusieurs anomalies : user_id null en session (user[0]["id"]), equipment_id manquant dans les logs, double clé étrangère (DROP COLUMN). Implémentation page logs.py</t>
+  </si>
+  <si>
+    <t>Aide IA : débogage erreurs PostgREST</t>
+  </si>
+  <si>
+    <t>Affichage des logs dans les fiches équipement et utilisateur. Tests complets du système de journalisation</t>
+  </si>
+  <si>
+    <t>Rédaction des sections Implémentation (back-end, front-end, journalisation, Git) et Tests (environnement, 20 cas de test, résultats et corrections)</t>
+  </si>
+  <si>
+    <t>Aide IA : rédaction et structuration</t>
+  </si>
+  <si>
+    <t>Rédaction des sections Manuel d'exploitation, Manuel d'utilisation, Conclusion personnelle. Envoi du rendu aux experts et au chef de projet</t>
+  </si>
 </sst>
 </file>
 
@@ -386,7 +432,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,8 +514,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A7FA1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,8 +565,13 @@
         <bgColor rgb="FFECF0F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFDE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -577,11 +635,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDC3C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -624,23 +695,35 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -919,24 +1002,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1075,10 +1158,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="17"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>5:00</v>
@@ -1088,22 +1171,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1232,10 +1315,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="17"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>4:00</v>
@@ -1245,18 +1328,18 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="16"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>9:00</v>
@@ -1295,24 +1378,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1449,10 +1532,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="17"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>7:10</v>
@@ -1462,22 +1545,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1633,10 +1716,10 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="17"/>
+      <c r="B22" s="21"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>5:50</v>
@@ -1646,22 +1729,22 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
     </row>
     <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -1784,10 +1867,10 @@
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="17"/>
+      <c r="B32" s="21"/>
       <c r="C32" s="4" t="str">
         <f>TEXT(IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>5:35</v>
@@ -1797,22 +1880,22 @@
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -1941,10 +2024,10 @@
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="17"/>
+      <c r="B42" s="21"/>
       <c r="C42" s="4" t="str">
         <f>TEXT(IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -1954,18 +2037,18 @@
       <c r="F42" s="7"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="16"/>
+      <c r="B44" s="20"/>
       <c r="C44" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0)+IF(C32&lt;&gt;"",TIMEVALUE(C32),0)+IF(C42&lt;&gt;"",TIMEVALUE(C42),0),"[h]:mm")</f>
         <v>22:30</v>
@@ -2008,25 +2091,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2157,10 +2240,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="17"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>6:00</v>
@@ -2170,22 +2253,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2322,10 +2405,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="17"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>7:20</v>
@@ -2335,22 +2418,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -2487,10 +2570,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="17"/>
+      <c r="B31" s="21"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>6:25</v>
@@ -2500,22 +2583,22 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
     </row>
     <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -2644,10 +2727,10 @@
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="17"/>
+      <c r="B41" s="21"/>
       <c r="C41" s="4" t="str">
         <f>TEXT(IF(C35&lt;&gt;"",TIMEVALUE(C35),0)+IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -2657,18 +2740,18 @@
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="16"/>
+      <c r="B43" s="20"/>
       <c r="C43" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>23:40</v>
@@ -2711,25 +2794,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2885,10 +2968,10 @@
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="17"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>4:35</v>
@@ -2898,22 +2981,22 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -3050,10 +3133,10 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="17"/>
+      <c r="B22" s="21"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>7:25</v>
@@ -3063,38 +3146,38 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="16"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="8" t="str">
         <f>TEXT(IF(C12&lt;&gt;"",TIMEVALUE(C12),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0),"[h]:mm")</f>
         <v>12:00</v>
@@ -3134,25 +3217,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3174,102 +3257,152 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.40972222222222221</v>
+      </c>
       <c r="C5" s="4" t="str">
         <f t="shared" ref="C5:C10" si="0">IF(AND(A5&lt;&gt;"",B5&lt;&gt;""),TEXT(B5-A5,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+        <v>1:35</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C6" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+        <v>2:25</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.56944444444444442</v>
+      </c>
       <c r="C7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+        <v>0:20</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.625</v>
+      </c>
       <c r="C8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+        <v>1:15</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="11"/>
+    </row>
+    <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.68402777777777779</v>
+      </c>
       <c r="C9" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+        <v>1:20</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="C10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+        <v>0:15</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="17"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>7:10</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -3291,102 +3424,156 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+    <row r="15" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>0.34375</v>
+      </c>
+      <c r="B15" s="16">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="C15" s="4" t="str">
-        <f t="shared" ref="C15:C20" si="1">IF(AND(A15&lt;&gt;"",B15&lt;&gt;""),TEXT(B15-A15,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+        <f t="shared" ref="C15:C18" si="1">IF(AND(A15&lt;&gt;"",B15&lt;&gt;""),TEXT(B15-A15,"[h]:mm"),"")</f>
+        <v>1:15</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="B16" s="16">
+        <v>0.4375</v>
+      </c>
       <c r="C16" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+        <v>0:55</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="B17" s="16">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="C17" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+        <v>1:55</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="B18" s="16">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="C18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+        <v>1:10</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="B19" s="16">
+        <v>0.65972222222222221</v>
+      </c>
       <c r="C19" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+        <f>IF(AND(A19&lt;&gt;"",B19&lt;&gt;""),TEXT(B19-A19,"[h]:mm"),"")</f>
+        <v>1:15</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="B20" s="16">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="C20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+        <f>IF(AND(A20&lt;&gt;"",B20&lt;&gt;""),TEXT(B20-A20,"[h]:mm"),"")</f>
+        <v>0:50</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="4" t="str">
+      <c r="B21" s="22"/>
+      <c r="C21" s="18" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>7:20</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -3475,10 +3662,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="17"/>
+      <c r="B31" s="21"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>0:00</v>
@@ -3488,21 +3675,21 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="16"/>
+      <c r="B33" s="20"/>
       <c r="C33" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>14:30</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -3522,7 +3709,7 @@
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A31:B31"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
+++ b/Documents/LAM_Jimmy-journal-travail-TPI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pk74hjc\Desktop\TPI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36174463-D009-48CC-AF56-F89C73B040EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D314508-5AB1-4ECE-92D1-75E1DC407E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Semaine 3'!$A$1:$F$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Semaine 4'!$A$1:$F$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Semaine 5'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Semaine 5'!$A$1:$F$33</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="130">
   <si>
     <t>TPI - Journal de travail | Semaine 1 - Jeudi 23 - Vendredi 24 avril 2026</t>
   </si>
@@ -424,13 +424,35 @@
   <si>
     <t>Rédaction des sections Manuel d'exploitation, Manuel d'utilisation, Conclusion personnelle. Envoi du rendu aux experts et au chef de projet</t>
   </si>
+  <si>
+    <t>Corrections de la documentation : suppression de la phrase informelle sur la connexion dans la Conclusion, reformulation du ton familier dans l'installation et la page Equipements. Mise à jour de la table des matières</t>
+  </si>
+  <si>
+    <t>Correction bug OCR double-rendu : remplacement du widget camera_input or file_uploader par un radio button. Correction auth.py : ajout log login_failed, déplacement import log_action en haut du fichier. Correction users.py : require_role(["admin"]) au lieu de require_role("admin")</t>
+  </si>
+  <si>
+    <t>IA utilisée pour identifier la cause du double-rendu Streamlit et du UnboundLocalError dans auth.py</t>
+  </si>
+  <si>
+    <t>Relecture complète de la documentation, vérification de la cohérence avec le code final. Ajout de la section suivi des risques dans la Partie 1. Export PDF et vérification finale du rendu</t>
+  </si>
+  <si>
+    <t>Remplissage et finalisation du journal de travail — dernier jour du TPI</t>
+  </si>
+  <si>
+    <t>Corrections de la documentation : déplacement du Résumé en tête de Partie 2, déplacement de la Conclusion personnelle dans la Partie 1</t>
+  </si>
+  <si>
+    <t>Rendu du TPI final</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="h:mm"/>
+    <numFmt numFmtId="165" formatCode="h:mm:ss"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -652,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -702,6 +724,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -1002,24 +1027,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1158,10 +1183,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>5:00</v>
@@ -1171,22 +1196,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1315,10 +1340,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="21"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>4:00</v>
@@ -1328,18 +1353,18 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="20"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>9:00</v>
@@ -1378,24 +1403,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1532,10 +1557,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>7:10</v>
@@ -1545,22 +1570,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1716,10 +1741,10 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="21"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>5:50</v>
@@ -1729,22 +1754,22 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -1867,10 +1892,10 @@
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="21"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="4" t="str">
         <f>TEXT(IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
         <v>5:35</v>
@@ -1880,22 +1905,22 @@
       <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -2024,10 +2049,10 @@
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="21"/>
+      <c r="B42" s="22"/>
       <c r="C42" s="4" t="str">
         <f>TEXT(IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -2037,18 +2062,18 @@
       <c r="F42" s="7"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="19"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="20"/>
+      <c r="B44" s="21"/>
       <c r="C44" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0)+IF(C32&lt;&gt;"",TIMEVALUE(C32),0)+IF(C42&lt;&gt;"",TIMEVALUE(C42),0),"[h]:mm")</f>
         <v>22:30</v>
@@ -2091,25 +2116,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2240,10 +2265,10 @@
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>6:00</v>
@@ -2253,22 +2278,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2405,10 +2430,10 @@
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="21"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>7:20</v>
@@ -2418,22 +2443,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -2570,10 +2595,10 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="21"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
         <v>6:25</v>
@@ -2583,22 +2608,22 @@
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
     </row>
     <row r="34" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -2727,10 +2752,10 @@
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="21"/>
+      <c r="B41" s="22"/>
       <c r="C41" s="4" t="str">
         <f>TEXT(IF(C35&lt;&gt;"",TIMEVALUE(C35),0)+IF(C36&lt;&gt;"",TIMEVALUE(C36),0)+IF(C37&lt;&gt;"",TIMEVALUE(C37),0)+IF(C38&lt;&gt;"",TIMEVALUE(C38),0)+IF(C39&lt;&gt;"",TIMEVALUE(C39),0)+IF(C40&lt;&gt;"",TIMEVALUE(C40),0),"[h]:mm")</f>
         <v>3:55</v>
@@ -2740,18 +2765,18 @@
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
     </row>
     <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="20"/>
+      <c r="B43" s="21"/>
       <c r="C43" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0)+IF(C41&lt;&gt;"",TIMEVALUE(C41),0),"[h]:mm")</f>
         <v>23:40</v>
@@ -2794,25 +2819,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -2968,10 +2993,10 @@
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>4:35</v>
@@ -2981,22 +3006,22 @@
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
     </row>
     <row r="15" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -3133,10 +3158,10 @@
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="21"/>
+      <c r="B22" s="22"/>
       <c r="C22" s="4" t="str">
         <f>TEXT(IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0),"[h]:mm")</f>
         <v>7:25</v>
@@ -3146,38 +3171,38 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="20"/>
+      <c r="B26" s="21"/>
       <c r="C26" s="8" t="str">
         <f>TEXT(IF(C12&lt;&gt;"",TIMEVALUE(C12),0)+IF(C22&lt;&gt;"",TIMEVALUE(C22),0),"[h]:mm")</f>
         <v>12:00</v>
@@ -3217,25 +3242,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -3374,10 +3399,10 @@
       <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4" t="str">
         <f>TEXT(IF(C5&lt;&gt;"",TIMEVALUE(C5),0)+IF(C6&lt;&gt;"",TIMEVALUE(C6),0)+IF(C7&lt;&gt;"",TIMEVALUE(C7),0)+IF(C8&lt;&gt;"",TIMEVALUE(C8),0)+IF(C9&lt;&gt;"",TIMEVALUE(C9),0)+IF(C10&lt;&gt;"",TIMEVALUE(C10),0),"[h]:mm")</f>
         <v>7:10</v>
@@ -3387,22 +3412,22 @@
       <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -3545,10 +3570,10 @@
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="22"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="18" t="str">
         <f>TEXT(IF(C15&lt;&gt;"",TIMEVALUE(C15),0)+IF(C16&lt;&gt;"",TIMEVALUE(C16),0)+IF(C17&lt;&gt;"",TIMEVALUE(C17),0)+IF(C18&lt;&gt;"",TIMEVALUE(C18),0)+IF(C19&lt;&gt;"",TIMEVALUE(C19),0)+IF(C20&lt;&gt;"",TIMEVALUE(C20),0),"[h]:mm")</f>
         <v>7:20</v>
@@ -3558,22 +3583,22 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
@@ -3595,101 +3620,151 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+    <row r="25" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>0.34375</v>
+      </c>
+      <c r="B25" s="19">
+        <v>0.40972222222222199</v>
+      </c>
       <c r="C25" s="4" t="str">
         <f t="shared" ref="C25:C30" si="2">IF(AND(A25&lt;&gt;"",B25&lt;&gt;""),TEXT(B25-A25,"[h]:mm"),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+        <v>1:35</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>0.42013888888888901</v>
+      </c>
+      <c r="B26" s="19">
+        <v>0.45138888888888901</v>
+      </c>
       <c r="C26" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+        <v>0:45</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>0.55555555555555602</v>
+      </c>
+      <c r="B27" s="19">
+        <v>0.60416666666666696</v>
+      </c>
       <c r="C27" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+        <v>1:10</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>0.60763888888888895</v>
+      </c>
+      <c r="B28" s="19">
+        <v>0.62152777777777779</v>
+      </c>
       <c r="C28" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+        <v>0:20</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="B29" s="19">
+        <v>0.63194444444444442</v>
+      </c>
       <c r="C29" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+        <v>0:05</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>0.63194444444444442</v>
+      </c>
+      <c r="B30" s="19">
+        <v>0.63888888888888884</v>
+      </c>
       <c r="C30" s="4" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+        <v>0:10</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="21"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="4" t="str">
         <f>TEXT(IF(C25&lt;&gt;"",TIMEVALUE(C25),0)+IF(C26&lt;&gt;"",TIMEVALUE(C26),0)+IF(C27&lt;&gt;"",TIMEVALUE(C27),0)+IF(C28&lt;&gt;"",TIMEVALUE(C28),0)+IF(C29&lt;&gt;"",TIMEVALUE(C29),0)+IF(C30&lt;&gt;"",TIMEVALUE(C30),0),"[h]:mm")</f>
-        <v>0:00</v>
+        <v>4:05</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
     </row>
     <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="20"/>
+      <c r="B33" s="21"/>
       <c r="C33" s="8" t="str">
         <f>TEXT(IF(C11&lt;&gt;"",TIMEVALUE(C11),0)+IF(C21&lt;&gt;"",TIMEVALUE(C21),0)+IF(C31&lt;&gt;"",TIMEVALUE(C31),0),"[h]:mm")</f>
-        <v>14:30</v>
+        <v>18:35</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
